--- a/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תאיר מרציאנו - מחרוזת קיץ 2026</v>
+        <v>ששון שאולוב – נווה הדרים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410768&amp;sid=32c601c210b460583a1c8e7094286233</v>
+        <v>https://yosmusic.com/%d7%a9%d7%a9%d7%95%d7%9f-%d7%a9%d7%90%d7%95%d7%9c%d7%95%d7%91-%d7%a0%d7%95%d7%95%d7%94-%d7%94%d7%93%d7%a8%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>ששון שאולוב הוא ממובילי הגל החדש של הפופ־המזרחי הרומנטי בישראל: מדובר בשירים שמבוססים פחות על תחכום מוזיקלי ויותר על רגש ישיר, פגיעות גברית והגשה “שבורה” כמעט במכוון. "נווה הדרים" הוא שיר אהבה טוטאלי, מוגזם, מתמסר ולפעמים אפילו מתבכיין, אבל בדיוק</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,164 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תאיר מרציאנו - מחרוזת קיץ 2026</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שניר כהן - מה קורה לי</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-08</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410767&amp;sid=32c601c210b460583a1c8e7094286233</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-08</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שניר כהן - מה קורה לי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>שימי תבורי - את כלה</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-08</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410766&amp;sid=32c601c210b460583a1c8e7094286233</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-08</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>שימי תבורי - את כלה</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>שי בסיל - נשף מסכות</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-08</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410765&amp;sid=32c601c210b460583a1c8e7094286233</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-08</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>שי בסיל - נשף מסכות</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>אנה זק – ילד שמנת</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-08</v>
-      </c>
-      <c r="C6" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a0%d7%94-%d7%96%d7%a7-%d7%99%d7%9c%d7%93-%d7%a9%d7%9e%d7%a0%d7%aa/</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-08</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v>אנה זק עושה פופ ציני, נוצץ ומודע לעצמו, שמצליח לקחת דמות מאוד מוכרת מהתרבות הישראלית – הילד העשיר שחי באינסטגרם, ולהפוך אותה לקריקטורה קצבית וממכרת. הדמות בשיר היא לא אדם ספציפי  אלא טיפוס: בן עשירים, חי באסתטיקה של רשתות חברתיות,</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>אנה זק – ילד שמנת</v>
+        <v>ששון שאולוב – נווה הדרים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ששון שאולוב – נווה הדרים</v>
+        <v>שלומי ימין - רוקדת</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%a9%d7%95%d7%9f-%d7%a9%d7%90%d7%95%d7%9c%d7%95%d7%91-%d7%a0%d7%95%d7%95%d7%94-%d7%94%d7%93%d7%a8%d7%99%d7%9d/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410793&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-09</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>ששון שאולוב הוא ממובילי הגל החדש של הפופ־המזרחי הרומנטי בישראל: מדובר בשירים שמבוססים פחות על תחכום מוזיקלי ויותר על רגש ישיר, פגיעות גברית והגשה “שבורה” כמעט במכוון. "נווה הדרים" הוא שיר אהבה טוטאלי, מוגזם, מתמסר ולפעמים אפילו מתבכיין, אבל בדיוק</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,544 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ששון שאולוב – נווה הדרים</v>
+        <v>שלומי ימין - רוקדת</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שלומי ימין - הגבר של חיי</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410792&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שלומי ימין - הגבר של חיי</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>שלומי ימין - בַּלֵּילוֹת כְּשֶׁהָעוֹלָם סוֹעֵר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410791&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>שלומי ימין - בַּלֵּילוֹת כְּשֶׁהָעוֹלָם סוֹעֵר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>שירז אברהם - אבא תודה - גרסה אקוסטית</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410790&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>שירז אברהם - אבא תודה - גרסה אקוסטית</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>רגב הוד - מחרוזת יותר מידי שנים 2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410789&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>רגב הוד - מחרוזת יותר מידי שנים 2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>עדי עייש - דופק אותי הגעגוע</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410788&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>עדי עייש - דופק אותי הגעגוע</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ניב אבוטבול - הפרויקט של הדיכאון של ניב 2 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410787&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>ניב אבוטבול - הפרויקט של הדיכאון של ניב 2 2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>מושיקו מור - אלינור</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410786&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>מושיקו מור - אלינור</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ירין פרחן - עיניים עצובות קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410785&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>ירין פרחן - עיניים עצובות קאבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>זכי צברי - מחרוזת לֵגֶה אוֹטִי תֵ'ס לֵגֶה 2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410784&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>זכי צברי - מחרוזת לֵגֶה אוֹטִי תֵ'ס לֵגֶה 2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>הדר אבני &amp; דקלה תפילין - שם טבעת</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410783&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>הדר אבני &amp; דקלה תפילין - שם טבעת</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>דנה עדיני - אהבה טהורה</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410782&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>דנה עדיני - אהבה טהורה</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אלסי דול - 00:00 (אמאלה)</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410781&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אלסי דול - 00:00 (אמאלה)</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אור משה - אבא</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410780&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אור משה - אבא</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אבי חן - Toy Muborak</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410779&amp;sid=0eb4dee345209cc006e0fa55481c77be</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-05-09</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אבי חן - Toy Muborak</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עידו מלכה – טפטופים</v>
+        <v>מתן לוי – ילדה אחת</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%99%d7%93%d7%95-%d7%9e%d7%9c%d7%9b%d7%94-%d7%98%d7%a4%d7%98%d7%95%d7%a4%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%aa%d7%9f-%d7%9c%d7%95%d7%99-%d7%99%d7%9c%d7%93%d7%94-%d7%90%d7%97%d7%aa/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-10</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "טפטופים” של עידו מלכה עובד קודם כול בזכות הניגודיות שבו – מצד אחד כאב רגשי ובלבול, מצד שני ביטים קלילים, משחקי מילים ופזמון שנתקע בראש. זה שיר על אובססיה רומנטית, תלות רגשית והתבגרות אחרי קשר סוער. “עברתי כבר את</v>
+        <v>מתן לוי שר בלדת רוק על רעב להכרה, בריחה מהכאב ומחיר התהילה. הוא מצליח לשלב בין רגש אישי מאוד לבין הפקה גדולה ודרמטית, וזה מה שנותן לו כוח. השיר על ילדה שבאה משבר – “אמא כאן אבא שם כמה יש</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עידו מלכה – טפטופים</v>
+        <v>מתן לוי – ילדה אחת</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מתן לוי – ילדה אחת</v>
+        <v>שמואל - שיר אהבה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%aa%d7%9f-%d7%9c%d7%95%d7%99-%d7%99%d7%9c%d7%93%d7%94-%d7%90%d7%97%d7%aa/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410806&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-10</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מתן לוי שר בלדת רוק על רעב להכרה, בריחה מהכאב ומחיר התהילה. הוא מצליח לשלב בין רגש אישי מאוד לבין הפקה גדולה ודרמטית, וזה מה שנותן לו כוח. השיר על ילדה שבאה משבר – “אמא כאן אבא שם כמה יש</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,468 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מתן לוי – ילדה אחת</v>
+        <v>שמואל - שיר אהבה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>קרולינה &amp; אורי בראונר כנרות - תפילה</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410805&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>קרולינה &amp; אורי בראונר כנרות - תפילה</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>קארין שוקרי - זאת שמרצה</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410804&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>קארין שוקרי - זאת שמרצה</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>עדן חסון - כל הברכה שלי</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410803&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>עדן חסון - כל הברכה שלי</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>נועה קירל - הכי יפה כשטעים לך</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410802&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>נועה קירל - הכי יפה כשטעים לך</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>ג'קו אייזנברג &amp; רון נשר - קיווינו</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410801&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>ג'קו אייזנברג &amp; רון נשר - קיווינו</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>גוסטו - אל תלכי לי מאמי לאיבוד</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410800&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>גוסטו - אל תלכי לי מאמי לאיבוד</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>בן גדסי - נסיכה בלי נסיכים</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410799&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>בן גדסי - נסיכה בלי נסיכים</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אריאל רייכל - אדון עולם</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410798&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אריאל רייכל - אדון עולם</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אסף הרוש - להרים עיניים</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410797&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אסף הרוש - להרים עיניים</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אליה והב - ירושלים</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410796&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אליה והב - ירושלים</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אור בר - מתוק או מר</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410795&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אור בר - מתוק או מר</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אופיר כלב - כאן איתי</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410794&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אופיר כלב - כאן איתי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמואל - שיר אהבה</v>
+        <v>אבבה – Mother</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410806&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%91%d7%94-mother/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר 'Mother” של אבבה AvevA הוא הרבה מעבר לבלדת נשמה. זה שיר קינה, תפילה, חיבוק ומחאה בו־זמנית.הוא מצליח לקחת כאב קולקטיבי של אימהות, של קהילה ושל טראומה מתמשכת ולהפוך אותו לחוויה מוזיקלית שיש בה גם חמלה וגם כוח רוחני. זה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמואל - שיר אהבה</v>
+        <v>אבבה – Mother</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>קרולינה &amp; אורי בראונר כנרות - תפילה</v>
+        <v>עדן חסון – כל הברכה שלי</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410805&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%97%d7%a1%d7%95%d7%9f-%d7%9b%d7%9c-%d7%94%d7%91%d7%a8%d7%9b%d7%94-%d7%a9%d7%9c%d7%99/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>"כל הברכה שלי” של עדן חסון הוא שיר אהבה ים תיכוני שנשען כמעט כולו על רגש ישיר ולא מתוחכם. הוא לא מנסה להיות פיוטי, מורכב או חדשני אלא להעביר תחושת אהבה טוטאלית, חמה ומנחמת בצורה הכי נגישה שיש. הפשטות הזאת</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,27 +507,27 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>קרולינה &amp; אורי בראונר כנרות - תפילה</v>
+        <v>עדן חסון – כל הברכה שלי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>קארין שוקרי - זאת שמרצה</v>
+        <v>יערה לוי – קיטשי</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410804&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+        <v>https://yosmusic.com/%d7%99%d7%a2%d7%a8%d7%94-%d7%9c%d7%95%d7%99-%d7%a7%d7%99%d7%98%d7%a9%d7%99/</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>השיר "קיטשי” של יערה לוי הוא שיר פופ־מידטמפו שמצליח לעשות משהו עדין ומעניין: לקחת רגש שנתפס כ"מביך" או "נאיבי" – הרצון לרומנטיקה אמיתית, ולהפוך אותו להצהרה מודעת לעצמה. הוא לא צוחק על הקיטש, אבל גם לא נופל אליו לגמרי. במקום</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -545,27 +545,27 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>קארין שוקרי - זאת שמרצה</v>
+        <v>יערה לוי – קיטשי</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עדן חסון - כל הברכה שלי</v>
+        <v>נועה קירל – הכי יפה כשטעים לך</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410803&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
+        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%94-%d7%a7%d7%99%d7%a8%d7%9c-%d7%94%d7%9b%d7%99-%d7%99%d7%a4%d7%94-%d7%9b%d7%a9%d7%98%d7%a2%d7%99%d7%9d-%d7%9c%d7%9a/</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>נועה קירל דוהרת על פופ־דאנס קליל שעוסק בנושא טעון: יחסי נשים עם אוכל, משקל ודימוי גוף.כותבי השיר אינם  מטיפים ולא נכנסים לדרמה כבדה  אלא משתמשים בהומור, גרוב ואנרגיה צעירה כדי לדבר על חרדה מאוד יומיומית. זה שיר ביט דאנס קופצני,</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -583,354 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עדן חסון - כל הברכה שלי</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>נועה קירל - הכי יפה כשטעים לך</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410802&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>נועה קירל - הכי יפה כשטעים לך</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>ג'קו אייזנברג &amp; רון נשר - קיווינו</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410801&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>ג'קו אייזנברג &amp; רון נשר - קיווינו</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>גוסטו - אל תלכי לי מאמי לאיבוד</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410800&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>גוסטו - אל תלכי לי מאמי לאיבוד</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>בן גדסי - נסיכה בלי נסיכים</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410799&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>בן גדסי - נסיכה בלי נסיכים</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אריאל רייכל - אדון עולם</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410798&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אריאל רייכל - אדון עולם</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אסף הרוש - להרים עיניים</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410797&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אסף הרוש - להרים עיניים</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אליה והב - ירושלים</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410796&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אליה והב - ירושלים</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אור בר - מתוק או מר</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410795&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אור בר - מתוק או מר</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>אופיר כלב - כאן איתי</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410794&amp;sid=8124153d5960992a8b9e8cc94efe762a</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>אופיר כלב - כאן איתי</v>
+        <v>נועה קירל – הכי יפה כשטעים לך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אבבה – Mother</v>
+        <v>קלניא - מחרוזת ציפור זרה 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%91%d7%94-mother/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410817&amp;sid=382252bd0582108617b18f9601d68d2b</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-11</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר 'Mother” של אבבה AvevA הוא הרבה מעבר לבלדת נשמה. זה שיר קינה, תפילה, חיבוק ומחאה בו־זמנית.הוא מצליח לקחת כאב קולקטיבי של אימהות, של קהילה ושל טראומה מתמשכת ולהפוך אותו לחוויה מוזיקלית שיש בה גם חמלה וגם כוח רוחני. זה</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אבבה – Mother</v>
+        <v>קלניא - מחרוזת ציפור זרה 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עדן חסון – כל הברכה שלי</v>
+        <v>קלניא - עד יום מותי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-11</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%97%d7%a1%d7%95%d7%9f-%d7%9b%d7%9c-%d7%94%d7%91%d7%a8%d7%9b%d7%94-%d7%a9%d7%9c%d7%99/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410816&amp;sid=382252bd0582108617b18f9601d68d2b</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-11</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>"כל הברכה שלי” של עדן חסון הוא שיר אהבה ים תיכוני שנשען כמעט כולו על רגש ישיר ולא מתוחכם. הוא לא מנסה להיות פיוטי, מורכב או חדשני אלא להעביר תחושת אהבה טוטאלית, חמה ומנחמת בצורה הכי נגישה שיש. הפשטות הזאת</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עדן חסון – כל הברכה שלי</v>
+        <v>קלניא - עד יום מותי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יערה לוי – קיטשי</v>
+        <v>פרחי ירושלים - ירושלים</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-11</v>
       </c>
       <c r="C4" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%a2%d7%a8%d7%94-%d7%9c%d7%95%d7%99-%d7%a7%d7%99%d7%98%d7%a9%d7%99/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410815&amp;sid=382252bd0582108617b18f9601d68d2b</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-11</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>השיר "קיטשי” של יערה לוי הוא שיר פופ־מידטמפו שמצליח לעשות משהו עדין ומעניין: לקחת רגש שנתפס כ"מביך" או "נאיבי" – הרצון לרומנטיקה אמיתית, ולהפוך אותו להצהרה מודעת לעצמה. הוא לא צוחק על הקיטש, אבל גם לא נופל אליו לגמרי. במקום</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יערה לוי – קיטשי</v>
+        <v>פרחי ירושלים - ירושלים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נועה קירל – הכי יפה כשטעים לך</v>
+        <v>עומר צמח - לב מדבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-11</v>
       </c>
       <c r="C5" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%94-%d7%a7%d7%99%d7%a8%d7%9c-%d7%94%d7%9b%d7%99-%d7%99%d7%a4%d7%94-%d7%9b%d7%a9%d7%98%d7%a2%d7%99%d7%9d-%d7%9c%d7%9a/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410814&amp;sid=382252bd0582108617b18f9601d68d2b</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-11</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>נועה קירל דוהרת על פופ־דאנס קליל שעוסק בנושא טעון: יחסי נשים עם אוכל, משקל ודימוי גוף.כותבי השיר אינם  מטיפים ולא נכנסים לדרמה כבדה  אלא משתמשים בהומור, גרוב ואנרגיה צעירה כדי לדבר על חרדה מאוד יומיומית. זה שיר ביט דאנס קופצני,</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -583,12 +583,240 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נועה קירל – הכי יפה כשטעים לך</v>
+        <v>עומר צמח - לב מדבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מיה כהן - כביסה מלוכלכת</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410813&amp;sid=382252bd0582108617b18f9601d68d2b</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מיה כהן - כביסה מלוכלכת</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>זנטי - זזה</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410812&amp;sid=382252bd0582108617b18f9601d68d2b</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>זנטי - זזה</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>זואי דגן - משמעות אחרת</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410811&amp;sid=382252bd0582108617b18f9601d68d2b</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>זואי דגן - משמעות אחרת</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>דודו טסה - אביב בחוץ</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410810&amp;sid=382252bd0582108617b18f9601d68d2b</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>דודו טסה - אביב בחוץ</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>גיא זהבי &amp; אורי שוחט - משוך בחבל</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410809&amp;sid=382252bd0582108617b18f9601d68d2b</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>גיא זהבי &amp; אורי שוחט - משוך בחבל</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אסתר גד - תלוי ועומד</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410808&amp;sid=382252bd0582108617b18f9601d68d2b</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אסתר גד - תלוי ועומד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קלניא - מחרוזת ציפור זרה 2026</v>
+        <v>מתן חסן (המסתערב) לא מפחד</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410817&amp;sid=382252bd0582108617b18f9601d68d2b</v>
+        <v>https://yosmusic.com/%d7%9e%d7%aa%d7%9f-%d7%97%d7%a1%d7%9f-%d7%94%d7%9e%d7%a1%d7%aa%d7%a2%d7%a8%d7%91-%d7%9c%d7%90-%d7%9e%d7%a4%d7%97%d7%93/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>המקדם של השיר – הפער בין הדימוי שממנו הגיע  “המסתערב במסכה”  לבין החשיפה הרגשית .של השיר עצמו. מצד שני: במקום שיר כוחני או הירואי, מתן חסן מביא בלדת פופ־ים־תיכונית שמבוססת על פגיעות, חרדה קיומית וחיפוש עצמי. זה שיר על אדם</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,354 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קלניא - מחרוזת ציפור זרה 2026</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>קלניא - עד יום מותי</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410816&amp;sid=382252bd0582108617b18f9601d68d2b</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>קלניא - עד יום מותי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>פרחי ירושלים - ירושלים</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410815&amp;sid=382252bd0582108617b18f9601d68d2b</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>פרחי ירושלים - ירושלים</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>עומר צמח - לב מדבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410814&amp;sid=382252bd0582108617b18f9601d68d2b</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>עומר צמח - לב מדבר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>מיה כהן - כביסה מלוכלכת</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410813&amp;sid=382252bd0582108617b18f9601d68d2b</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>מיה כהן - כביסה מלוכלכת</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>זנטי - זזה</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410812&amp;sid=382252bd0582108617b18f9601d68d2b</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>זנטי - זזה</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>זואי דגן - משמעות אחרת</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410811&amp;sid=382252bd0582108617b18f9601d68d2b</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>זואי דגן - משמעות אחרת</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>דודו טסה - אביב בחוץ</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410810&amp;sid=382252bd0582108617b18f9601d68d2b</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>דודו טסה - אביב בחוץ</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>גיא זהבי &amp; אורי שוחט - משוך בחבל</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410809&amp;sid=382252bd0582108617b18f9601d68d2b</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>גיא זהבי &amp; אורי שוחט - משוך בחבל</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אסתר גד - תלוי ועומד</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410808&amp;sid=382252bd0582108617b18f9601d68d2b</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אסתר גד - תלוי ועומד</v>
+        <v>מתן חסן (המסתערב) לא מפחד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מתן חסן (המסתערב) לא מפחד</v>
+        <v>אופיר סלומון - מה נהיה ממני</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-12</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%aa%d7%9f-%d7%97%d7%a1%d7%9f-%d7%94%d7%9e%d7%a1%d7%aa%d7%a2%d7%a8%d7%91-%d7%9c%d7%90-%d7%9e%d7%a4%d7%97%d7%93/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410819&amp;sid=678301c7d441635eca10ba6cfbe7b50e</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-12</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>המקדם של השיר – הפער בין הדימוי שממנו הגיע  “המסתערב במסכה”  לבין החשיפה הרגשית .של השיר עצמו. מצד שני: במקום שיר כוחני או הירואי, מתן חסן מביא בלדת פופ־ים־תיכונית שמבוססת על פגיעות, חרדה קיומית וחיפוש עצמי. זה שיר על אדם</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,88 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מתן חסן (המסתערב) לא מפחד</v>
+        <v>אופיר סלומון - מה נהיה ממני</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אודי דמארי - ניגון שלווה</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410818&amp;sid=678301c7d441635eca10ba6cfbe7b50e</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אודי דמארי - ניגון שלווה</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>אלדד ציטרין ואדר גולד – פורטרט</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C4" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%9c%d7%93%d7%93-%d7%a6%d7%99%d7%98%d7%a8%d7%99%d7%9f-%d7%95%d7%90%d7%93%d7%a8-%d7%92%d7%95%d7%9c%d7%93-%d7%a4%d7%95%d7%a8%d7%98%d7%a8%d7%98/</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>אדר גולד ואלדד ציטרין מבצעים בלדה מינורית שקטה ומכאיבה שעוסקת באחד מסוגי הגעגוע המורכבים ביותר: געגוע למישהו שכמעט לא הספקת להכיר. זה שיר על זיכרון חסר, על ניסיון לבנות דמות מתוך סיפורים, חפצים ורסיסי נוכחות. במקום להתאבל על מה שהיה,</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>אלדד ציטרין ואדר גולד – פורטרט</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אופיר סלומון - מה נהיה ממני</v>
+        <v>עמית אשכנזי - אין לך מקום</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-12</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410819&amp;sid=678301c7d441635eca10ba6cfbe7b50e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410836&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-12</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אופיר סלומון - מה נהיה ממני</v>
+        <v>עמית אשכנזי - אין לך מקום</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אודי דמארי - ניגון שלווה</v>
+        <v>עומר דוד - מהמזרח לתל אביב</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-12</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410818&amp;sid=678301c7d441635eca10ba6cfbe7b50e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410835&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-12</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אודי דמארי - ניגון שלווה</v>
+        <v>עומר דוד - מהמזרח לתל אביב</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אלדד ציטרין ואדר גולד – פורטרט</v>
+        <v>נהוראי רחמימוב - איתי כאן לעד</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-12</v>
       </c>
       <c r="C4" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%9c%d7%93%d7%93-%d7%a6%d7%99%d7%98%d7%a8%d7%99%d7%9f-%d7%95%d7%90%d7%93%d7%a8-%d7%92%d7%95%d7%9c%d7%93-%d7%a4%d7%95%d7%a8%d7%98%d7%a8%d7%98/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410834&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-12</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>אדר גולד ואלדד ציטרין מבצעים בלדה מינורית שקטה ומכאיבה שעוסקת באחד מסוגי הגעגוע המורכבים ביותר: געגוע למישהו שכמעט לא הספקת להכיר. זה שיר על זיכרון חסר, על ניסיון לבנות דמות מתוך סיפורים, חפצים ורסיסי נוכחות. במקום להתאבל על מה שהיה,</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -545,12 +545,544 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אלדד ציטרין ואדר גולד – פורטרט</v>
+        <v>נהוראי רחמימוב - איתי כאן לעד</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מן יהל - נשבר לי</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410833&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מן יהל - נשבר לי</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ישראל בן חמו - בר יוחאי יסוד עולם</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410832&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>ישראל בן חמו - בר יוחאי יסוד עולם</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>שחר טבוך &amp; מאיה דדון - הנסיך של רמת גן</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410831&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>שחר טבוך &amp; מאיה דדון - הנסיך של רמת גן</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>מתי שריקי - מזמור לתודה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410830&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>מתי שריקי - מזמור לתודה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>מאי טוויק - שישרפו הקנאים</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410829&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>מאי טוויק - שישרפו הקנאים</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>יעקב הראל - מחרוזת אבא תודה 2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410828&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>יעקב הראל - מחרוזת אבא תודה 2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>יוחנן - שלום</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410827&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>יוחנן - שלום</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>חביב חיים בן אריה - אל מול הים</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410826&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>חביב חיים בן אריה - אל מול הים</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>דניאל בוחבוט - מחרוזת חצי לב 2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410825&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>דניאל בוחבוט - מחרוזת חצי לב 2026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>בן ימין - פריק של טעויות</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410824&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>בן ימין - פריק של טעויות</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אלעד אלדד &amp; ינון דודיאן - אני אוהב אותך</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410823&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אלעד אלדד &amp; ינון דודיאן - אני אוהב אותך</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אליה ביטון - מכאן זה לנצח</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410822&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אליה ביטון - מכאן זה לנצח</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>איתי בירמן &amp; אריאל זילבר - אשריכם</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410821&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>איתי בירמן &amp; אריאל זילבר - אשריכם</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>אילאי ברדה - חזק אני</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410820&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>אילאי ברדה - חזק אני</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עמית אשכנזי - אין לך מקום</v>
+        <v>שר-אל - מנגינות של כאב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-12</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410836&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410841&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-12</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עמית אשכנזי - אין לך מקום</v>
+        <v>שר-אל - מנגינות של כאב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עומר דוד - מהמזרח לתל אביב</v>
+        <v>שניר עזרן - אם רק תחזרי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-12</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410835&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410840&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-12</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עומר דוד - מהמזרח לתל אביב</v>
+        <v>שניר עזרן - אם רק תחזרי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נהוראי רחמימוב - איתי כאן לעד</v>
+        <v>שלומי ימין - אין על מה לחשוב</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-12</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410834&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410839&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-12</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נהוראי רחמימוב - איתי כאן לעד</v>
+        <v>שלומי ימין - אין על מה לחשוב</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מן יהל - נשבר לי</v>
+        <v>שי וינר - כנפי השכינה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-12</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410833&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410838&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-12</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מן יהל - נשבר לי</v>
+        <v>שי וינר - כנפי השכינה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ישראל בן חמו - בר יוחאי יסוד עולם</v>
+        <v>עמית סמוכי - קצת נשימה</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-12</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410832&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410837&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-12</v>
@@ -621,468 +621,12 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ישראל בן חמו - בר יוחאי יסוד עולם</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>שחר טבוך &amp; מאיה דדון - הנסיך של רמת גן</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410831&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>שחר טבוך &amp; מאיה דדון - הנסיך של רמת גן</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>מתי שריקי - מזמור לתודה</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410830&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>מתי שריקי - מזמור לתודה</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>מאי טוויק - שישרפו הקנאים</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410829&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>מאי טוויק - שישרפו הקנאים</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>יעקב הראל - מחרוזת אבא תודה 2026</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410828&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>יעקב הראל - מחרוזת אבא תודה 2026</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>יוחנן - שלום</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410827&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>יוחנן - שלום</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>חביב חיים בן אריה - אל מול הים</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410826&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>חביב חיים בן אריה - אל מול הים</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>דניאל בוחבוט - מחרוזת חצי לב 2026</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410825&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>דניאל בוחבוט - מחרוזת חצי לב 2026</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>בן ימין - פריק של טעויות</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410824&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>בן ימין - פריק של טעויות</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>אלעד אלדד &amp; ינון דודיאן - אני אוהב אותך</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410823&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>אלעד אלדד &amp; ינון דודיאן - אני אוהב אותך</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>אליה ביטון - מכאן זה לנצח</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410822&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v>אליה ביטון - מכאן זה לנצח</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>איתי בירמן &amp; אריאל זילבר - אשריכם</v>
-      </c>
-      <c r="B17" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410821&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D17" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
-        <v>איתי בירמן &amp; אריאל זילבר - אשריכם</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>אילאי ברדה - חזק אני</v>
-      </c>
-      <c r="B18" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410820&amp;sid=4febdd71f1044df3bf7d1c8fbc0fa718</v>
-      </c>
-      <c r="D18" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
-        <v>אילאי ברדה - חזק אני</v>
+        <v>עמית סמוכי - קצת נשימה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שר-אל - מנגינות של כאב</v>
+        <v>מאי טוויק – שישרפו הקנאים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410841&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%99-%d7%98%d7%95%d7%95%d7%99%d7%a7-%d7%a9%d7%99%d7%a9%d7%a8%d7%a4%d7%95-%d7%94%d7%a7%d7%a0%d7%90%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>"שישרפו הקנאים" של מאי טוויק בנוי כמו מסלול רגשי שמתפתח בהדרגה – מבלדה אינטימית ושבורה אל התפרצות EDM רגשית, כמעט קתרזיס של כאב. זה לא רק שינוי מוזיקלי – המעברים עצמם הם חלק מהסיפור. הפתיחה יושבת על קול נמוך, כמעט</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,164 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שר-אל - מנגינות של כאב</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שניר עזרן - אם רק תחזרי</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410840&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שניר עזרן - אם רק תחזרי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>שלומי ימין - אין על מה לחשוב</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410839&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>שלומי ימין - אין על מה לחשוב</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>שי וינר - כנפי השכינה</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410838&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>שי וינר - כנפי השכינה</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>עמית סמוכי - קצת נשימה</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410837&amp;sid=2dca41cca0759bf32b087ba630e29016</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>עמית סמוכי - קצת נשימה</v>
+        <v>מאי טוויק – שישרפו הקנאים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מאי טוויק – שישרפו הקנאים</v>
+        <v>עילי בוטנר והילדים החדשים – גם בנים בוכים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-13</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%99-%d7%98%d7%95%d7%95%d7%99%d7%a7-%d7%a9%d7%99%d7%a9%d7%a8%d7%a4%d7%95-%d7%94%d7%a7%d7%a0%d7%90%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%99%d7%9c%d7%99-%d7%91%d7%95%d7%98%d7%a0%d7%a8-%d7%95%d7%94%d7%99%d7%9c%d7%93%d7%99%d7%9d-%d7%94%d7%97%d7%93%d7%a9%d7%99%d7%9d-%d7%92%d7%9d-%d7%91%d7%a0%d7%99%d7%9d-%d7%91%d7%95%d7%9b%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-13</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"שישרפו הקנאים" של מאי טוויק בנוי כמו מסלול רגשי שמתפתח בהדרגה – מבלדה אינטימית ושבורה אל התפרצות EDM רגשית, כמעט קתרזיס של כאב. זה לא רק שינוי מוזיקלי – המעברים עצמם הם חלק מהסיפור. הפתיחה יושבת על קול נמוך, כמעט</v>
+        <v>"גם בנים בוכים" של עילי בוטנר והילדים החדשים בנוי כפופ מלודי מידטמפו שמתפתח בהדרגה  לא דרך דרופ חד או התפרצות דרמטית, אלא דרך הצטברות רגשית איטית, כמעט קולנועית. זה שיר שנע כמו נסיעה לילית ארוכה: כביש פתוח, אורות חולפים, מחשבות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מאי טוויק – שישרפו הקנאים</v>
+        <v>עילי בוטנר והילדים החדשים – גם בנים בוכים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עילי בוטנר והילדים החדשים – גם בנים בוכים</v>
+        <v>שחר טבוך ומאיה דדון – הנסיך של רמת גן</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%99%d7%9c%d7%99-%d7%91%d7%95%d7%98%d7%a0%d7%a8-%d7%95%d7%94%d7%99%d7%9c%d7%93%d7%99%d7%9d-%d7%94%d7%97%d7%93%d7%a9%d7%99%d7%9d-%d7%92%d7%9d-%d7%91%d7%a0%d7%99%d7%9d-%d7%91%d7%95%d7%9b%d7%99/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%97%d7%a8-%d7%98%d7%91%d7%95%d7%9a-%d7%95%d7%9e%d7%90%d7%99%d7%94-%d7%93%d7%93%d7%95%d7%9f-%d7%94%d7%a0%d7%a1%d7%99%d7%9a-%d7%a9%d7%9c-%d7%a8%d7%9e%d7%aa-%d7%92%d7%9f/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"גם בנים בוכים" של עילי בוטנר והילדים החדשים בנוי כפופ מלודי מידטמפו שמתפתח בהדרגה  לא דרך דרופ חד או התפרצות דרמטית, אלא דרך הצטברות רגשית איטית, כמעט קולנועית. זה שיר שנע כמו נסיעה לילית ארוכה: כביש פתוח, אורות חולפים, מחשבות</v>
+        <v>הנסיך של רמת גן של שחר טבוך ומאיה דדון הוא פופ ים־תיכוני צבעוני, קאמפי ומודע לעצמו, שמצליח להפוך מעבר דירה לרמת גן למיתולוגיה פופית קטנה.זה שיר שלא מנסה להיות “עמוק”  אלא כריזמטי, מצחיק, פלרטטני ומאוד מודע לתרבות הרשת והטיקטוק. שחר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עילי בוטנר והילדים החדשים – גם בנים בוכים</v>
+        <v>שחר טבוך ומאיה דדון – הנסיך של רמת גן</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שחר טבוך ומאיה דדון – הנסיך של רמת גן</v>
+        <v>ליעד אלון - כולי תפילה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-14</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%97%d7%a8-%d7%98%d7%91%d7%95%d7%9a-%d7%95%d7%9e%d7%90%d7%99%d7%94-%d7%93%d7%93%d7%95%d7%9f-%d7%94%d7%a0%d7%a1%d7%99%d7%9a-%d7%a9%d7%9c-%d7%a8%d7%9e%d7%aa-%d7%92%d7%9f/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410873&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-14</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הנסיך של רמת גן של שחר טבוך ומאיה דדון הוא פופ ים־תיכוני צבעוני, קאמפי ומודע לעצמו, שמצליח להפוך מעבר דירה לרמת גן למיתולוגיה פופית קטנה.זה שיר שלא מנסה להיות “עמוק”  אלא כריזמטי, מצחיק, פלרטטני ומאוד מודע לתרבות הרשת והטיקטוק. שחר</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,278 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שחר טבוך ומאיה דדון – הנסיך של רמת גן</v>
+        <v>ליעד אלון - כולי תפילה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>לינור דהן - דור צמא</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410872&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>לינור דהן - דור צמא</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ירין נקטלוב - תכף הענן יחלוף</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410871&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>ירין נקטלוב - תכף הענן יחלוף</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>חיים יהודה מארח את דוד יהודה - אורך כבר יאיר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410870&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>חיים יהודה מארח את דוד יהודה - אורך כבר יאיר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>זואי דגן - גשרים</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410869&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>זואי דגן - גשרים</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>דניאל אזולאי - מחרוזת חשמל באויר 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410868&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>דניאל אזולאי - מחרוזת חשמל באויר 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>דוד ברג - זה לטובה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410867&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>דוד ברג - זה לטובה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אורי זר - תמיד בלב אמא</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410866&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אורי זר - תמיד בלב אמא</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליעד אלון - כולי תפילה</v>
+        <v>יהודה בורן &amp; נתנאל אמסילי - ירושלים קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-14</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410873&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410880&amp;sid=f4fe23e3870234ea0a746e91c15ef66d</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-14</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליעד אלון - כולי תפילה</v>
+        <v>יהודה בורן &amp; נתנאל אמסילי - ירושלים קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>לינור דהן - דור צמא</v>
+        <v>אלינור מנו - מנגינה שקטה</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-14</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410872&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410879&amp;sid=f4fe23e3870234ea0a746e91c15ef66d</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-14</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>לינור דהן - דור צמא</v>
+        <v>אלינור מנו - מנגינה שקטה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ירין נקטלוב - תכף הענן יחלוף</v>
+        <v>תמר ריילי - אמן אמן אמן</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-14</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410871&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410878&amp;sid=f4fe23e3870234ea0a746e91c15ef66d</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-14</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ירין נקטלוב - תכף הענן יחלוף</v>
+        <v>תמר ריילי - אמן אמן אמן</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>חיים יהודה מארח את דוד יהודה - אורך כבר יאיר</v>
+        <v>צדי אור - שיק תימני</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-14</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410870&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410877&amp;sid=f4fe23e3870234ea0a746e91c15ef66d</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-14</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>חיים יהודה מארח את דוד יהודה - אורך כבר יאיר</v>
+        <v>צדי אור - שיק תימני</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>זואי דגן - גשרים</v>
+        <v>עילי בוטנר והילדים החדשים - גם בנים בוכים</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-14</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410869&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410876&amp;sid=f4fe23e3870234ea0a746e91c15ef66d</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-14</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>זואי דגן - גשרים</v>
+        <v>עילי בוטנר והילדים החדשים - גם בנים בוכים</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>דניאל אזולאי - מחרוזת חשמל באויר 2026</v>
+        <v>נתנאל ברדה - אחד שלא עוזב (ירושלים)</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-14</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410868&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410875&amp;sid=f4fe23e3870234ea0a746e91c15ef66d</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-14</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>דניאל אזולאי - מחרוזת חשמל באויר 2026</v>
+        <v>נתנאל ברדה - אחד שלא עוזב (ירושלים)</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>דוד ברג - זה לטובה</v>
+        <v>מוטי אוריאל - ירושלים</v>
       </c>
       <c r="B8" t="str">
         <v>2026-05-14</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410867&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410874&amp;sid=f4fe23e3870234ea0a746e91c15ef66d</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-14</v>
@@ -697,50 +697,12 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>דוד ברג - זה לטובה</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אורי זר - תמיד בלב אמא</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-14</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410866&amp;sid=22644b10625591dd2fda856f09d4cdc7</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-14</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אורי זר - תמיד בלב אמא</v>
+        <v>מוטי אוריאל - ירושלים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>